--- a/data/trending_integrated_20261029_13.xlsx
+++ b/data/trending_integrated_20261029_13.xlsx
@@ -578,7 +578,7 @@
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F2" t="n">
         <v>26</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>6843263319</v>
+        <v>6846324209</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -619,7 +619,7 @@
         <v>2900</v>
       </c>
       <c r="R2" t="n">
-        <v>3000</v>
+        <v>-2000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9350</v>
+        <v>9390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.02%</t>
+          <t>'+17.52%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G3" t="n">
         <v>82</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>126383847490</v>
+        <v>126797230155</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -711,10 +711,10 @@
         <v>1760</v>
       </c>
       <c r="R3" t="n">
-        <v>66000</v>
+        <v>-19000</v>
       </c>
       <c r="S3" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38050</v>
+        <v>38100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.34%</t>
+          <t>'+9.48%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H4" t="n">
         <v>5.8</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>108842064100</v>
+        <v>109476906850</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -803,10 +803,10 @@
         <v>15260</v>
       </c>
       <c r="R4" t="n">
-        <v>91000</v>
+        <v>89000</v>
       </c>
       <c r="S4" t="n">
-        <v>37000</v>
+        <v>39000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7860</v>
+        <v>7820</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.50%</t>
+          <t>'+4.97%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F5" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G5" t="n">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>105871421885</v>
+        <v>106637928045</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -895,7 +895,7 @@
         <v>952</v>
       </c>
       <c r="R5" t="n">
-        <v>290000</v>
+        <v>10000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1513000</v>
+        <v>1512500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.75%</t>
+          <t>'+1.71%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G6" t="n">
-        <v>1241</v>
+        <v>1269</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.61</v>
       </c>
       <c r="O6" t="n">
-        <v>4961981702500</v>
+        <v>5042151372000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -987,14 +987,14 @@
         <v>501000</v>
       </c>
       <c r="R6" t="n">
-        <v>337000</v>
+        <v>357000</v>
       </c>
       <c r="S6" t="n">
-        <v>-93000</v>
+        <v>-139000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자 대비 상대적 강세 및 시가총액 역전 기대감. 신용대출 및 외인 매수세 언급.</t>
+          <t>삼성전자와 차별화된 흐름 분석, 외인 매수세 유입. 반도체 업황 긍정적 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['하이닉스', '삼성전자', '시가총액']</t>
+          <t>['삼성전자', '외인매수', '반도체']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,10 +1038,10 @@
         <v>0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
         <v>76</v>
@@ -1070,7 +1070,7 @@
         <v>1.73</v>
       </c>
       <c r="O7" t="n">
-        <v>102030270250</v>
+        <v>102372817050</v>
       </c>
       <c r="P7" t="n">
         <v>59600</v>
@@ -1079,10 +1079,10 @@
         <v>1850</v>
       </c>
       <c r="R7" t="n">
-        <v>44000</v>
+        <v>-52000</v>
       </c>
       <c r="S7" t="n">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14430</v>
+        <v>14450</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.28%</t>
+          <t>'+0.42%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F8" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G8" t="n">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="H8" t="n">
         <v>8.050000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>53072410070</v>
+        <v>53312026280</v>
       </c>
       <c r="P8" t="n">
         <v>49800</v>
@@ -1171,23 +1171,23 @@
         <v>8180</v>
       </c>
       <c r="R8" t="n">
-        <v>-238000</v>
+        <v>-290000</v>
       </c>
       <c r="S8" t="n">
-        <v>11000</v>
+        <v>-6000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 의료 AI 섹터 강세와 연동된 주가 변동성. 공매도 및 단기 세력 이탈 가능성 언급.</t>
+          <t>의료 AI 관련 미국 시장 동향 언급. 차트 및 공매도 관련 분석.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['의료AI', '공매도', '단기세력']</t>
+          <t>['의료AI', '미국시장', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,70 +1207,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14870</v>
+        <v>533000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.73%</t>
+          <t>'-0.19%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.46</v>
+        <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>145</v>
+        <v>343</v>
       </c>
       <c r="F9" t="n">
-        <v>84</v>
+        <v>171</v>
       </c>
       <c r="G9" t="n">
-        <v>801</v>
+        <v>1753</v>
       </c>
       <c r="H9" t="n">
-        <v>3.33</v>
+        <v>24.78</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14980</v>
+        <v>534000</v>
       </c>
       <c r="K9" t="n">
-        <v>15120</v>
+        <v>546000</v>
       </c>
       <c r="L9" t="n">
-        <v>15950</v>
+        <v>563000</v>
       </c>
       <c r="M9" t="n">
-        <v>14600</v>
+        <v>512000</v>
       </c>
       <c r="N9" t="n">
-        <v>2.87</v>
+        <v>24.86</v>
       </c>
       <c r="O9" t="n">
-        <v>141842747145</v>
+        <v>472297181500</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>723000</v>
       </c>
       <c r="Q9" t="n">
-        <v>1819</v>
+        <v>259000</v>
       </c>
       <c r="R9" t="n">
-        <v>-312000</v>
+        <v>-39000</v>
       </c>
       <c r="S9" t="n">
-        <v>42000</v>
+        <v>27000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>메타버스 관련 뉴스 및 루멘텀 인수설, 삼성전자 투자 가능성 제기. 연말 목표가 3만 제시.</t>
+          <t>3분기 호실적 달성 및 컨센서스 상회. 전고체 배터리 상용화 기대감 반영.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['메타버스', '루멘텀', '삼성전자']</t>
+          <t>['실적', '컨퍼런스콜', '전고체배터리']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>006400</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>529000</v>
+        <v>14880</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.94%</t>
+          <t>'-0.67%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.08</v>
+        <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>337</v>
+        <v>146</v>
       </c>
       <c r="F10" t="n">
-        <v>168</v>
+        <v>85</v>
       </c>
       <c r="G10" t="n">
-        <v>1717</v>
+        <v>815</v>
       </c>
       <c r="H10" t="n">
-        <v>24.78</v>
+        <v>3.33</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>534000</v>
+        <v>14980</v>
       </c>
       <c r="K10" t="n">
-        <v>546000</v>
+        <v>15120</v>
       </c>
       <c r="L10" t="n">
-        <v>563000</v>
+        <v>15950</v>
       </c>
       <c r="M10" t="n">
-        <v>512000</v>
+        <v>14600</v>
       </c>
       <c r="N10" t="n">
-        <v>24.86</v>
+        <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>465479047500</v>
+        <v>142521317345</v>
       </c>
       <c r="P10" t="n">
-        <v>723000</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>259000</v>
+        <v>1819</v>
       </c>
       <c r="R10" t="n">
-        <v>-24000</v>
+        <v>-464000</v>
       </c>
       <c r="S10" t="n">
-        <v>9000</v>
+        <v>44000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>삼성SDI, 3분기 호실적 및 컨퍼런스콜 내용 기반 향후 전망 긍정적. 전고체 배터리 상용화 기대감.</t>
+          <t>메타버스 관련 뉴스 및 루멘텀 인수설, 삼성전자 투자 가능성 제기. 연말 목표가 3만 제시.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['컨퍼런스콜', '전고체 배터리', '실적']</t>
+          <t>['메타버스', '루멘텀', '삼성전자']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>62900</v>
+        <v>63200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.02%</t>
+          <t>'-1.56%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.54</v>
       </c>
       <c r="E11" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F11" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G11" t="n">
-        <v>596</v>
+        <v>616</v>
       </c>
       <c r="H11" t="n">
         <v>41.55</v>
@@ -1438,7 +1438,7 @@
         <v>41.01</v>
       </c>
       <c r="O11" t="n">
-        <v>152625751150</v>
+        <v>154725025600</v>
       </c>
       <c r="P11" t="n">
         <v>67300</v>
@@ -1447,10 +1447,10 @@
         <v>23150</v>
       </c>
       <c r="R11" t="n">
-        <v>408000</v>
+        <v>436000</v>
       </c>
       <c r="S11" t="n">
-        <v>-60000</v>
+        <v>-150000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26150</v>
+        <v>26200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.06%</t>
+          <t>'-1.87%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G12" t="n">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="H12" t="n">
         <v>12.23</v>
@@ -1530,7 +1530,7 @@
         <v>12.3</v>
       </c>
       <c r="O12" t="n">
-        <v>37464690700</v>
+        <v>37791790400</v>
       </c>
       <c r="P12" t="n">
         <v>59300</v>
@@ -1539,7 +1539,7 @@
         <v>22000</v>
       </c>
       <c r="R12" t="n">
-        <v>-80000</v>
+        <v>-142000</v>
       </c>
       <c r="S12" t="n">
         <v>-15000</v>
@@ -1596,7 +1596,7 @@
         <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H13" t="n">
         <v>0.37</v>
@@ -1622,7 +1622,7 @@
         <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>30173480390</v>
+        <v>30233201460</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1631,10 +1631,10 @@
         <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-47000</v>
+        <v>-42000</v>
       </c>
       <c r="S13" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>182800</v>
+        <v>183000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.84%</t>
+          <t>'-3.73%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G14" t="n">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="H14" t="n">
         <v>75</v>
@@ -1714,7 +1714,7 @@
         <v>74.90000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>1210606672100</v>
+        <v>1224664621250</v>
       </c>
       <c r="P14" t="n">
         <v>243500</v>
@@ -1723,14 +1723,14 @@
         <v>71000</v>
       </c>
       <c r="R14" t="n">
-        <v>-409000</v>
+        <v>-1183000</v>
       </c>
       <c r="S14" t="n">
-        <v>-172000</v>
+        <v>-148000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>이재용 증여세 이슈와 연관된 주주환원 불확실성 및 IR 내용에 대한 불만 제기.</t>
+          <t>오너 리스크 및 초저가 IR 비판. 주주 환원 불확실성 및 컨퍼런스 콜 내용에 대한 불만.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['증여세', '주주환원', 'IR']</t>
+          <t>['오너리스크', '주주환원', 'IR']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,83 +1759,83 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4015</v>
+        <v>15830</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.29%</t>
+          <t>'-4.12%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="F15" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G15" t="n">
-        <v>341</v>
+        <v>420</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2</v>
+        <v>28.07</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4195</v>
+        <v>16510</v>
       </c>
       <c r="K15" t="n">
-        <v>4280</v>
+        <v>16380</v>
       </c>
       <c r="L15" t="n">
-        <v>4480</v>
+        <v>16440</v>
       </c>
       <c r="M15" t="n">
-        <v>3915</v>
+        <v>15750</v>
       </c>
       <c r="N15" t="n">
-        <v>1.2</v>
+        <v>28.03</v>
       </c>
       <c r="O15" t="n">
-        <v>163805700527</v>
+        <v>47102040670</v>
       </c>
       <c r="P15" t="n">
-        <v>8100</v>
+        <v>35350</v>
       </c>
       <c r="Q15" t="n">
-        <v>592</v>
+        <v>15750</v>
       </c>
       <c r="R15" t="n">
-        <v>-190000</v>
+        <v>-22000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-310000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>5G 상용화 및 글로벌 기업 공급 시작 관련 뉴스 부각. 광통신 섹터 강세와 연관.</t>
+          <t>실적 발표 후 주가 하락 및 조선주 전반에 대한 부정적 전망. 중국과의 경쟁력 약화 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['5G', '광통신', '공급']</t>
+          <t>['실적', '조선주', '중국']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15760</v>
+        <v>4005</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.54%</t>
+          <t>'-4.53%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>154</v>
+        <v>102</v>
       </c>
       <c r="F16" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G16" t="n">
-        <v>413</v>
+        <v>350</v>
       </c>
       <c r="H16" t="n">
-        <v>28.07</v>
+        <v>2.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>16510</v>
+        <v>4195</v>
       </c>
       <c r="K16" t="n">
-        <v>16380</v>
+        <v>4280</v>
       </c>
       <c r="L16" t="n">
-        <v>16440</v>
+        <v>4480</v>
       </c>
       <c r="M16" t="n">
-        <v>15750</v>
+        <v>3915</v>
       </c>
       <c r="N16" t="n">
-        <v>28.03</v>
+        <v>1.2</v>
       </c>
       <c r="O16" t="n">
-        <v>46032450095</v>
+        <v>164065907971</v>
       </c>
       <c r="P16" t="n">
-        <v>35350</v>
+        <v>8100</v>
       </c>
       <c r="Q16" t="n">
-        <v>15750</v>
+        <v>592</v>
       </c>
       <c r="R16" t="n">
-        <v>-48000</v>
+        <v>-190000</v>
       </c>
       <c r="S16" t="n">
-        <v>-70000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>실적 발표 후 주가 하락 및 조선주 전반에 대한 부정적 전망. 중국과의 경쟁력 약화 우려.</t>
+          <t>5G 상용화 및 글로벌 기업 공급 관련 뉴스 언급. 광통신 섹터 주도주 가능성.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['실적', '조선주', '중국']</t>
+          <t>['5G', '광통신', '수주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>230500</v>
+        <v>229000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.75%</t>
+          <t>'-5.37%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="G17" t="n">
-        <v>2267</v>
+        <v>2226</v>
       </c>
       <c r="H17" t="n">
         <v>46.19</v>
@@ -1990,7 +1990,7 @@
         <v>46.15</v>
       </c>
       <c r="O17" t="n">
-        <v>4210726001000</v>
+        <v>4277261182500</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -1999,14 +1999,14 @@
         <v>94500</v>
       </c>
       <c r="R17" t="n">
-        <v>-197000</v>
+        <v>-434000</v>
       </c>
       <c r="S17" t="n">
-        <v>15000</v>
+        <v>-387000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>이재용 증여세 이슈와 함께 주가 하락 및 주주환원 불만 제기. 컨퍼런스콜 내용에 대한 비판.</t>
+          <t>컨퍼런스 콜 내용에 대한 경영진 비판 및 주주 환원 불만 표출. 증여세 이슈와 연관된 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['증여세', '주주환원', '컨퍼런스콜']</t>
+          <t>['컨퍼런스콜', '주주환원', '증여세']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,184 +2035,184 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1856</v>
+        <v>54500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-11.62%</t>
+          <t>'-11.24%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.28</v>
+        <v>0.02</v>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>554</v>
       </c>
       <c r="G18" t="n">
-        <v>153</v>
+        <v>2148</v>
       </c>
       <c r="H18" t="n">
-        <v>5.35</v>
+        <v>22.34</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2100</v>
+        <v>61400</v>
       </c>
       <c r="K18" t="n">
-        <v>2120</v>
+        <v>60600</v>
       </c>
       <c r="L18" t="n">
-        <v>2130</v>
+        <v>60800</v>
       </c>
       <c r="M18" t="n">
-        <v>1846</v>
+        <v>53400</v>
       </c>
       <c r="N18" t="n">
-        <v>5.07</v>
+        <v>22.32</v>
       </c>
       <c r="O18" t="n">
-        <v>12830152556</v>
+        <v>301975020500</v>
       </c>
       <c r="P18" t="n">
-        <v>4980</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>810</v>
+        <v>53400</v>
       </c>
       <c r="R18" t="n">
-        <v>43000</v>
+        <v>-1454000</v>
       </c>
       <c r="S18" t="n">
-        <v>10000</v>
+        <v>-731000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>세계 최초 고방사 세라믹 코팅 로봇 개발 관련 국책 프로젝트 선정 뉴스 언급. 투자 심리 위축 및 매도세 강한 모습.</t>
+          <t>체코 원전 사업 협상 결렬에 대한 분석. 시공사 변경 이슈로 인한 영향 미미 전망. 기자재 계약 유지.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['로봇', '국책 프로젝트']</t>
+          <t>['체코 원전', '협상결렬', '기자재']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>53900</v>
+        <v>1849</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-12.21%</t>
+          <t>'-11.95%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.02</v>
+        <v>0.28</v>
       </c>
       <c r="E19" t="n">
-        <v>800</v>
+        <v>66</v>
       </c>
       <c r="F19" t="n">
-        <v>562</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>2174</v>
+        <v>157</v>
       </c>
       <c r="H19" t="n">
-        <v>22.34</v>
+        <v>5.35</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>61400</v>
+        <v>2100</v>
       </c>
       <c r="K19" t="n">
-        <v>60600</v>
+        <v>2120</v>
       </c>
       <c r="L19" t="n">
-        <v>60800</v>
+        <v>2130</v>
       </c>
       <c r="M19" t="n">
-        <v>53400</v>
+        <v>1846</v>
       </c>
       <c r="N19" t="n">
-        <v>22.32</v>
+        <v>5.07</v>
       </c>
       <c r="O19" t="n">
-        <v>295959951250</v>
+        <v>12987683606</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>4980</v>
       </c>
       <c r="Q19" t="n">
-        <v>53400</v>
+        <v>810</v>
       </c>
       <c r="R19" t="n">
-        <v>-1122000</v>
+        <v>-82000</v>
       </c>
       <c r="S19" t="n">
-        <v>-389000</v>
+        <v>10000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>체코 원전 사업 시공사 변경 이슈에 대한 혼란 및 분석. 두산에너빌리티 자체는 기자재 공급사로 직접적인 영향이 적다는 의견. 정부 정책 및 정치권 개입에 대한 비판.</t>
+          <t>세계 최초 고방사 세라믹 코팅 로봇 개발 관련 국책 프로젝트 선정 뉴스 언급. 투자 심리 위축 및 매도세 강한 모습.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['체코 원전', '시공사 변경', '기자재 공급']</t>
+          <t>['로봇', '국책 프로젝트']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16550</v>
+        <v>16430</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-13.85%</t>
+          <t>'-14.47%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F20" t="n">
         <v>60</v>
       </c>
       <c r="G20" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H20" t="n">
         <v>0.65</v>
@@ -2266,7 +2266,7 @@
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>90557213160</v>
+        <v>91039467690</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2275,23 +2275,23 @@
         <v>11550</v>
       </c>
       <c r="R20" t="n">
-        <v>47000</v>
+        <v>23000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>보호예수 물량 부담 및 단기 급락 가능성 경고. 공매도 및 주포 이탈 가능성 언급.</t>
+          <t>보호예수 물량 해제에 따른 급락 가능성 경고. 반도체 업황 둔화 우려.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['보호예수', '급락', '공매도']</t>
+          <t>['보호예수', '반도체', '급락']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11610</v>
+        <v>11780</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-18.64%</t>
+          <t>'-17.45%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2329,10 +2329,10 @@
         <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G21" t="n">
-        <v>2241</v>
+        <v>2312</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -2358,7 +2358,7 @@
         <v>9.83</v>
       </c>
       <c r="O21" t="n">
-        <v>288222107025</v>
+        <v>293713141280</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2367,14 +2367,14 @@
         <v>3320</v>
       </c>
       <c r="R21" t="n">
-        <v>224000</v>
+        <v>-695000</v>
       </c>
       <c r="S21" t="n">
-        <v>-957000</v>
+        <v>-1386000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>원전 사업 관련 불확실성 속에서 외국인 매수세 유입. 정치적 개입 및 재협상 가능성 언급.</t>
+          <t>체코 원전 수주 관련 단기 악재 인식, 과매도 분석. 외인 순매수 전환 추세 감지.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '협상', '외국인']</t>
+          <t>['체코 원전', '수주', '과매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2418,13 +2418,13 @@
         <v>-0.47</v>
       </c>
       <c r="E22" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G22" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H22" t="n">
         <v>1.22</v>
@@ -2450,7 +2450,7 @@
         <v>1.69</v>
       </c>
       <c r="O22" t="n">
-        <v>16168455871</v>
+        <v>16288818262</v>
       </c>
       <c r="P22" t="n">
         <v>2965</v>
@@ -2459,14 +2459,14 @@
         <v>865</v>
       </c>
       <c r="R22" t="n">
-        <v>-77000</v>
+        <v>-187000</v>
       </c>
       <c r="S22" t="n">
-        <v>-168000</v>
+        <v>-271000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>급격한 주가 하락 및 사기 의혹 제기. 실적 불확실성과 역망치 패턴 발생에 따른 투자자 불안감 고조.</t>
+          <t>실적 부진 및 주가 급락에 대한 우려 표출. 사채 발행 관련 정보 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['주가 하락', '사기 의혹', '역망치']</t>
+          <t>['실적', '주가급락', '사채']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20261029_13.xlsx
+++ b/data/trending_integrated_20261029_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F2" t="n">
         <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>6846324209</v>
+        <v>6862803959</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9390</v>
+        <v>9280</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.52%</t>
+          <t>'+16.15%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>63</v>
       </c>
       <c r="G3" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H3" t="n">
         <v>17.97</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>126797230155</v>
+        <v>127361078565</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>광통신 섹터 강세 속에서 주가 상승 기대감. 미국 루멘텀 폭등과 연관성 언급.</t>
+          <t>광통신 섹터 전반의 강세 및 개별 종목의 상승 여력에 대한 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['광통신', '루멘텀', '주가']</t>
+          <t>['광통신', '섹터 강세', '신규 진입']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38100</v>
+        <v>38300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.48%</t>
+          <t>'+10.06%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.74</v>
       </c>
       <c r="E4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F4" t="n">
         <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H4" t="n">
         <v>5.8</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>109476906850</v>
+        <v>110482947025</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7820</v>
+        <v>7890</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.97%</t>
+          <t>'+5.91%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="F5" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G5" t="n">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>106637928045</v>
+        <v>107003024695</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1512500</v>
+        <v>1528000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.71%</t>
+          <t>'+2.76%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>494</v>
       </c>
       <c r="G6" t="n">
-        <v>1269</v>
+        <v>1314</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.61</v>
       </c>
       <c r="O6" t="n">
-        <v>5042151372000</v>
+        <v>5170799331500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자와 차별화된 흐름 분석, 외인 매수세 유입. 반도체 업황 긍정적 전망.</t>
+          <t>삼성전자 대비 경쟁 우위 부각 및 시가총액 1위 달성 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['삼성전자', '외인매수', '반도체']</t>
+          <t>['경쟁 우위', '시가총액', '외국인 매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29050</v>
+        <v>29250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.22%</t>
+          <t>'+1.92%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H7" t="n">
         <v>1.77</v>
@@ -1070,7 +1070,7 @@
         <v>1.73</v>
       </c>
       <c r="O7" t="n">
-        <v>102372817050</v>
+        <v>103174238825</v>
       </c>
       <c r="P7" t="n">
         <v>59600</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14450</v>
+        <v>14410</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.42%</t>
+          <t>'+0.14%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F8" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G8" t="n">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="H8" t="n">
         <v>8.050000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>53312026280</v>
+        <v>53651424625</v>
       </c>
       <c r="P8" t="n">
         <v>49800</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>의료 AI 관련 미국 시장 동향 언급. 차트 및 공매도 관련 분석.</t>
+          <t>의료 AI 섹터 강세 및 공매도 세력에 대한 경고.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['의료AI', '미국시장', '공매도']</t>
+          <t>['의료 AI', '공매도', '헬스케어']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F9" t="n">
         <v>171</v>
       </c>
       <c r="G9" t="n">
-        <v>1753</v>
+        <v>1767</v>
       </c>
       <c r="H9" t="n">
         <v>24.78</v>
@@ -1254,7 +1254,7 @@
         <v>24.86</v>
       </c>
       <c r="O9" t="n">
-        <v>472297181500</v>
+        <v>478074067000</v>
       </c>
       <c r="P9" t="n">
         <v>723000</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14880</v>
+        <v>14940</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.67%</t>
+          <t>'-0.27%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F10" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G10" t="n">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="H10" t="n">
         <v>3.33</v>
@@ -1346,7 +1346,7 @@
         <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>142521317345</v>
+        <v>142944037355</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>63200</v>
+        <v>63500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.56%</t>
+          <t>'-1.09%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.54</v>
       </c>
       <c r="E11" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F11" t="n">
         <v>69</v>
       </c>
       <c r="G11" t="n">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="H11" t="n">
         <v>41.55</v>
@@ -1438,7 +1438,7 @@
         <v>41.01</v>
       </c>
       <c r="O11" t="n">
-        <v>154725025600</v>
+        <v>158803787500</v>
       </c>
       <c r="P11" t="n">
         <v>67300</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>수주 공시 및 신고가 도전 움직임. 삼성전자 투자 확대 뉴스와 건설 업종 내 상대적 강세 전망.</t>
+          <t>자사주 매입 및 소각 공시, 수주 소식에 따른 신고가 경신 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['수주 공시', '신고가', '삼성전자 투자']</t>
+          <t>['자사주 소각', '수주 공시', '신고가']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1504,7 +1504,7 @@
         <v>52</v>
       </c>
       <c r="G12" t="n">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="H12" t="n">
         <v>12.23</v>
@@ -1530,7 +1530,7 @@
         <v>12.3</v>
       </c>
       <c r="O12" t="n">
-        <v>37791790400</v>
+        <v>38147422825</v>
       </c>
       <c r="P12" t="n">
         <v>59300</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8900</v>
+        <v>8940</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.05%</t>
+          <t>'-2.61%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1622,7 +1622,7 @@
         <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>30233201460</v>
+        <v>30317981210</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>183000</v>
+        <v>184000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.73%</t>
+          <t>'-3.21%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F14" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G14" t="n">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="H14" t="n">
         <v>75</v>
@@ -1714,7 +1714,7 @@
         <v>74.90000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>1224664621250</v>
+        <v>1242683364200</v>
       </c>
       <c r="P14" t="n">
         <v>243500</v>
@@ -1759,70 +1759,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15830</v>
+        <v>4040</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.12%</t>
+          <t>'-3.69%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="F15" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G15" t="n">
-        <v>420</v>
+        <v>354</v>
       </c>
       <c r="H15" t="n">
-        <v>28.07</v>
+        <v>2.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>16510</v>
+        <v>4195</v>
       </c>
       <c r="K15" t="n">
-        <v>16380</v>
+        <v>4280</v>
       </c>
       <c r="L15" t="n">
-        <v>16440</v>
+        <v>4480</v>
       </c>
       <c r="M15" t="n">
-        <v>15750</v>
+        <v>3915</v>
       </c>
       <c r="N15" t="n">
-        <v>28.03</v>
+        <v>1.2</v>
       </c>
       <c r="O15" t="n">
-        <v>47102040670</v>
+        <v>164430976624</v>
       </c>
       <c r="P15" t="n">
-        <v>35350</v>
+        <v>8100</v>
       </c>
       <c r="Q15" t="n">
-        <v>15750</v>
+        <v>592</v>
       </c>
       <c r="R15" t="n">
-        <v>-22000</v>
+        <v>-190000</v>
       </c>
       <c r="S15" t="n">
-        <v>-310000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>실적 발표 후 주가 하락 및 조선주 전반에 대한 부정적 전망. 중국과의 경쟁력 약화 우려.</t>
+          <t>5G 상용화 및 글로벌 기업 공급 관련 뉴스 언급. 광통신 섹터 주도주 가능성.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['실적', '조선주', '중국']</t>
+          <t>['5G', '광통신', '수주']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4005</v>
+        <v>15850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.53%</t>
+          <t>'-4.00%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>102</v>
+        <v>162</v>
       </c>
       <c r="F16" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G16" t="n">
-        <v>350</v>
+        <v>433</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2</v>
+        <v>28.07</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4195</v>
+        <v>16510</v>
       </c>
       <c r="K16" t="n">
-        <v>4280</v>
+        <v>16380</v>
       </c>
       <c r="L16" t="n">
-        <v>4480</v>
+        <v>16440</v>
       </c>
       <c r="M16" t="n">
-        <v>3915</v>
+        <v>15750</v>
       </c>
       <c r="N16" t="n">
-        <v>1.2</v>
+        <v>28.03</v>
       </c>
       <c r="O16" t="n">
-        <v>164065907971</v>
+        <v>48498433915</v>
       </c>
       <c r="P16" t="n">
-        <v>8100</v>
+        <v>35350</v>
       </c>
       <c r="Q16" t="n">
-        <v>592</v>
+        <v>15750</v>
       </c>
       <c r="R16" t="n">
-        <v>-190000</v>
+        <v>-22000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-310000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>5G 상용화 및 글로벌 기업 공급 관련 뉴스 언급. 광통신 섹터 주도주 가능성.</t>
+          <t>실적 발표에 대한 부정적 전망 및 주가 하락 지속에 대한 우려.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['5G', '광통신', '수주']</t>
+          <t>['실적 발표', '주가 하락', '신저점']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>229000</v>
+        <v>230500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.37%</t>
+          <t>'-4.75%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>576</v>
+        <v>561</v>
       </c>
       <c r="G17" t="n">
-        <v>2226</v>
+        <v>2062</v>
       </c>
       <c r="H17" t="n">
         <v>46.19</v>
@@ -1990,7 +1990,7 @@
         <v>46.15</v>
       </c>
       <c r="O17" t="n">
-        <v>4277261182500</v>
+        <v>4359675256000</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>컨퍼런스 콜 내용에 대한 경영진 비판 및 주주 환원 불만 표출. 증여세 이슈와 연관된 주가 하락 우려.</t>
+          <t>컨퍼런스콜 미흡 및 주주환원 정책 비판. 경영진 교체 요구.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['컨퍼런스콜', '주주환원', '증여세']</t>
+          <t>['컨퍼런스콜', '주주환원', '경영진']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54500</v>
+        <v>54900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-11.24%</t>
+          <t>'-10.59%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="G18" t="n">
-        <v>2148</v>
+        <v>2118</v>
       </c>
       <c r="H18" t="n">
         <v>22.34</v>
@@ -2082,7 +2082,7 @@
         <v>22.32</v>
       </c>
       <c r="O18" t="n">
-        <v>301975020500</v>
+        <v>309700356700</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>체코 원전 사업 협상 결렬에 대한 분석. 시공사 변경 이슈로 인한 영향 미미 전망. 기자재 계약 유지.</t>
+          <t>체코 원전 사업 관련 불확실성에도 불구하고 기자재 계약은 유지된다는 분석.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['체코 원전', '협상결렬', '기자재']</t>
+          <t>['체코 원전', '기자재 계약', '협상 결렬']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1849</v>
+        <v>1834</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-11.95%</t>
+          <t>'-12.67%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>66</v>
       </c>
       <c r="F19" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H19" t="n">
         <v>5.35</v>
@@ -2168,13 +2168,13 @@
         <v>2130</v>
       </c>
       <c r="M19" t="n">
-        <v>1846</v>
+        <v>1824</v>
       </c>
       <c r="N19" t="n">
         <v>5.07</v>
       </c>
       <c r="O19" t="n">
-        <v>12987683606</v>
+        <v>13492471614</v>
       </c>
       <c r="P19" t="n">
         <v>4980</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16430</v>
+        <v>16580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-14.47%</t>
+          <t>'-13.69%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F20" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G20" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="H20" t="n">
         <v>0.65</v>
@@ -2266,7 +2266,7 @@
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>91039467690</v>
+        <v>91770078855</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>보호예수 물량 해제에 따른 급락 가능성 경고. 반도체 업황 둔화 우려.</t>
+          <t>보호예수 물량 출회에 따른 급락 가능성 경고.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['보호예수', '반도체', '급락']</t>
+          <t>['보호예수', '물량 출회', '급락']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11780</v>
+        <v>11740</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-17.45%</t>
+          <t>'-17.73%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2329,10 +2329,10 @@
         <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="G21" t="n">
-        <v>2312</v>
+        <v>2334</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -2358,7 +2358,7 @@
         <v>9.83</v>
       </c>
       <c r="O21" t="n">
-        <v>293713141280</v>
+        <v>299360638530</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>체코 원전 수주 관련 단기 악재 인식, 과매도 분석. 외인 순매수 전환 추세 감지.</t>
+          <t>체코 원전 사업 재협상 가능성 및 외국인 매수세 유입에 따른 단기 반등 기대.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['체코 원전', '수주', '과매도']</t>
+          <t>['체코 원전', '재협상', '외국인 매수']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2085</v>
+        <v>2095</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-18.87%</t>
+          <t>'-18.48%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.47</v>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F22" t="n">
         <v>62</v>
       </c>
       <c r="G22" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H22" t="n">
         <v>1.22</v>
@@ -2450,7 +2450,7 @@
         <v>1.69</v>
       </c>
       <c r="O22" t="n">
-        <v>16288818262</v>
+        <v>16405118182</v>
       </c>
       <c r="P22" t="n">
         <v>2965</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>실적 부진 및 주가 급락에 대한 우려 표출. 사채 발행 관련 정보 언급.</t>
+          <t>급격한 주가 하락 및 롤링 현상에 대한 불만.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['실적', '주가급락', '사채']</t>
+          <t>['주가 급락', '롤링', '사기']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20261029_13.xlsx
+++ b/data/trending_integrated_20261029_13.xlsx
@@ -584,7 +584,7 @@
         <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>6862803959</v>
+        <v>6867413179</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9280</v>
+        <v>9190</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.15%</t>
+          <t>'+15.02%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>63</v>
       </c>
       <c r="G3" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H3" t="n">
         <v>17.97</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>127361078565</v>
+        <v>128984333580</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>광통신 섹터 전반의 강세 및 개별 종목의 상승 여력에 대한 기대감.</t>
+          <t>광통신 섹터 내 대장주로서의 가능성 언급. 미국 시장 소폭 상승 및 루멘텀 급등 사례 참고.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['광통신', '섹터 강세', '신규 진입']</t>
+          <t>['광통신', '대장주', '루멘텀']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38300</v>
+        <v>38250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.06%</t>
+          <t>'+9.91%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.74</v>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
         <v>139</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>110482947025</v>
+        <v>111261305600</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7890</v>
+        <v>8030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.91%</t>
+          <t>'+7.79%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F5" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G5" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>107003024695</v>
+        <v>108650104600</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1528000</v>
+        <v>1529000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.76%</t>
+          <t>'+2.82%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="G6" t="n">
-        <v>1314</v>
+        <v>1381</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.61</v>
       </c>
       <c r="O6" t="n">
-        <v>5170799331500</v>
+        <v>5274765255000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자 대비 경쟁 우위 부각 및 시가총액 1위 달성 기대.</t>
+          <t>삼성전자 대비 경쟁 우위 확보 및 시총 1위 달성 전망. 4분기 실적 호조 기대감 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['경쟁 우위', '시가총액', '외국인 매수']</t>
+          <t>['경쟁 우위', '시총 1위', '실적 호조']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29250</v>
+        <v>29100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.92%</t>
+          <t>'+1.39%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H7" t="n">
         <v>1.77</v>
@@ -1070,7 +1070,7 @@
         <v>1.73</v>
       </c>
       <c r="O7" t="n">
-        <v>103174238825</v>
+        <v>103812101875</v>
       </c>
       <c r="P7" t="n">
         <v>59600</v>
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14410</v>
+        <v>537000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.14%</t>
+          <t>'+0.56%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>124</v>
+        <v>351</v>
       </c>
       <c r="F8" t="n">
-        <v>76</v>
+        <v>173</v>
       </c>
       <c r="G8" t="n">
-        <v>368</v>
+        <v>1800</v>
       </c>
       <c r="H8" t="n">
-        <v>8.050000000000001</v>
+        <v>24.78</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14390</v>
+        <v>534000</v>
       </c>
       <c r="K8" t="n">
-        <v>15450</v>
+        <v>546000</v>
       </c>
       <c r="L8" t="n">
-        <v>16290</v>
+        <v>563000</v>
       </c>
       <c r="M8" t="n">
-        <v>14040</v>
+        <v>512000</v>
       </c>
       <c r="N8" t="n">
-        <v>8.109999999999999</v>
+        <v>24.86</v>
       </c>
       <c r="O8" t="n">
-        <v>53651424625</v>
+        <v>489743997500</v>
       </c>
       <c r="P8" t="n">
-        <v>49800</v>
+        <v>723000</v>
       </c>
       <c r="Q8" t="n">
-        <v>8180</v>
+        <v>259000</v>
       </c>
       <c r="R8" t="n">
-        <v>-290000</v>
+        <v>-39000</v>
       </c>
       <c r="S8" t="n">
-        <v>-6000</v>
+        <v>27000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>의료 AI 섹터 강세 및 공매도 세력에 대한 경고.</t>
+          <t>3분기 호실적 달성 및 컨센서스 상회. 전고체 배터리 상용화 기대감 반영.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['의료 AI', '공매도', '헬스케어']</t>
+          <t>['실적', '컨퍼런스콜', '전고체배터리']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>006400</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>533000</v>
+        <v>14410</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.19%</t>
+          <t>'+0.14%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>345</v>
+        <v>126</v>
       </c>
       <c r="F9" t="n">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="G9" t="n">
-        <v>1767</v>
+        <v>375</v>
       </c>
       <c r="H9" t="n">
-        <v>24.78</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>534000</v>
+        <v>14390</v>
       </c>
       <c r="K9" t="n">
-        <v>546000</v>
+        <v>15450</v>
       </c>
       <c r="L9" t="n">
-        <v>563000</v>
+        <v>16290</v>
       </c>
       <c r="M9" t="n">
-        <v>512000</v>
+        <v>14040</v>
       </c>
       <c r="N9" t="n">
-        <v>24.86</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>478074067000</v>
+        <v>53987090745</v>
       </c>
       <c r="P9" t="n">
-        <v>723000</v>
+        <v>49800</v>
       </c>
       <c r="Q9" t="n">
-        <v>259000</v>
+        <v>8180</v>
       </c>
       <c r="R9" t="n">
-        <v>-39000</v>
+        <v>-290000</v>
       </c>
       <c r="S9" t="n">
-        <v>27000</v>
+        <v>-6000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3분기 호실적 달성 및 컨센서스 상회. 전고체 배터리 상용화 기대감 반영.</t>
+          <t>의료 AI 섹터 내 변동성 확대 및 공매도 관련 논란. 특정 가격대 이하 매수 구간 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['실적', '컨퍼런스콜', '전고체배터리']</t>
+          <t>['의료 AI', '공매도', '변동성']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14940</v>
+        <v>14920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.27%</t>
+          <t>'-0.40%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F10" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G10" t="n">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="H10" t="n">
         <v>3.33</v>
@@ -1346,7 +1346,7 @@
         <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>142944037355</v>
+        <v>143545127195</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1406,13 +1406,13 @@
         <v>0.54</v>
       </c>
       <c r="E11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F11" t="n">
         <v>69</v>
       </c>
       <c r="G11" t="n">
-        <v>624</v>
+        <v>640</v>
       </c>
       <c r="H11" t="n">
         <v>41.55</v>
@@ -1438,7 +1438,7 @@
         <v>41.01</v>
       </c>
       <c r="O11" t="n">
-        <v>158803787500</v>
+        <v>161622817800</v>
       </c>
       <c r="P11" t="n">
         <v>67300</v>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>자사주 매입 및 소각 공시, 수주 소식에 따른 신고가 경신 기대감.</t>
+          <t>자사주 매입 및 소각 기대감에 따른 주가 상승 전망. 수주 공시 및 신고가 도전 가능성 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26200</v>
+        <v>26300</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.87%</t>
+          <t>'-1.50%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G12" t="n">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="H12" t="n">
         <v>12.23</v>
@@ -1530,7 +1530,7 @@
         <v>12.3</v>
       </c>
       <c r="O12" t="n">
-        <v>38147422825</v>
+        <v>38539940800</v>
       </c>
       <c r="P12" t="n">
         <v>59300</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8940</v>
+        <v>8920</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.61%</t>
+          <t>'-2.83%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1622,7 +1622,7 @@
         <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>30317981210</v>
+        <v>30466041160</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>184000</v>
+        <v>16010</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.21%</t>
+          <t>'-3.03%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="F14" t="n">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="G14" t="n">
-        <v>504</v>
+        <v>446</v>
       </c>
       <c r="H14" t="n">
-        <v>75</v>
+        <v>28.07</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>190100</v>
+        <v>16510</v>
       </c>
       <c r="K14" t="n">
-        <v>189400</v>
+        <v>16380</v>
       </c>
       <c r="L14" t="n">
-        <v>197000</v>
+        <v>16440</v>
       </c>
       <c r="M14" t="n">
-        <v>180800</v>
+        <v>15750</v>
       </c>
       <c r="N14" t="n">
-        <v>74.90000000000001</v>
+        <v>28.03</v>
       </c>
       <c r="O14" t="n">
-        <v>1242683364200</v>
+        <v>51830670040</v>
       </c>
       <c r="P14" t="n">
-        <v>243500</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>71000</v>
+        <v>15750</v>
       </c>
       <c r="R14" t="n">
-        <v>-1183000</v>
+        <v>-22000</v>
       </c>
       <c r="S14" t="n">
-        <v>-148000</v>
+        <v>-310000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>오너 리스크 및 초저가 IR 비판. 주주 환원 불확실성 및 컨퍼런스 콜 내용에 대한 불만.</t>
+          <t>실적 발표에 대한 부정적 전망 및 주가 하락 지속에 대한 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['오너리스크', '주주환원', 'IR']</t>
+          <t>['실적 발표', '주가 하락', '신저점']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,86 +1752,86 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4040</v>
+        <v>184100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.69%</t>
+          <t>'-3.16%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>103</v>
+        <v>163</v>
       </c>
       <c r="F15" t="n">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="G15" t="n">
-        <v>354</v>
+        <v>542</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2</v>
+        <v>75</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4195</v>
+        <v>190100</v>
       </c>
       <c r="K15" t="n">
-        <v>4280</v>
+        <v>189400</v>
       </c>
       <c r="L15" t="n">
-        <v>4480</v>
+        <v>197000</v>
       </c>
       <c r="M15" t="n">
-        <v>3915</v>
+        <v>180800</v>
       </c>
       <c r="N15" t="n">
-        <v>1.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>164430976624</v>
+        <v>1257792237700</v>
       </c>
       <c r="P15" t="n">
-        <v>8100</v>
+        <v>243500</v>
       </c>
       <c r="Q15" t="n">
-        <v>592</v>
+        <v>71000</v>
       </c>
       <c r="R15" t="n">
-        <v>-190000</v>
+        <v>-1183000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-148000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>5G 상용화 및 글로벌 기업 공급 관련 뉴스 언급. 광통신 섹터 주도주 가능성.</t>
+          <t>주주 환원 불확실성 및 IR 발표 미흡에 대한 불만. 오너 리스크 및 증여세 관련 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['5G', '광통신', '수주']</t>
+          <t>['주주 환원', 'IR 발표', '오너 리스크']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15850</v>
+        <v>4020</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.00%</t>
+          <t>'-4.17%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>162</v>
+        <v>107</v>
       </c>
       <c r="F16" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G16" t="n">
-        <v>433</v>
+        <v>355</v>
       </c>
       <c r="H16" t="n">
-        <v>28.07</v>
+        <v>2.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>16510</v>
+        <v>4195</v>
       </c>
       <c r="K16" t="n">
-        <v>16380</v>
+        <v>4280</v>
       </c>
       <c r="L16" t="n">
-        <v>16440</v>
+        <v>4480</v>
       </c>
       <c r="M16" t="n">
-        <v>15750</v>
+        <v>3915</v>
       </c>
       <c r="N16" t="n">
-        <v>28.03</v>
+        <v>1.2</v>
       </c>
       <c r="O16" t="n">
-        <v>48498433915</v>
+        <v>164757568592</v>
       </c>
       <c r="P16" t="n">
-        <v>35350</v>
+        <v>8100</v>
       </c>
       <c r="Q16" t="n">
-        <v>15750</v>
+        <v>592</v>
       </c>
       <c r="R16" t="n">
-        <v>-22000</v>
+        <v>-190000</v>
       </c>
       <c r="S16" t="n">
-        <v>-310000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>실적 발표에 대한 부정적 전망 및 주가 하락 지속에 대한 우려.</t>
+          <t>5G 상용화 및 글로벌 기업 공급 관련 뉴스 언급. 광통신 섹터 주도주 가능성.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['실적 발표', '주가 하락', '신저점']</t>
+          <t>['5G', '광통신', '수주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>230500</v>
+        <v>230250</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.75%</t>
+          <t>'-4.86%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="G17" t="n">
-        <v>2062</v>
+        <v>2143</v>
       </c>
       <c r="H17" t="n">
         <v>46.19</v>
@@ -1990,7 +1990,7 @@
         <v>46.15</v>
       </c>
       <c r="O17" t="n">
-        <v>4359675256000</v>
+        <v>4423374987750</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>컨퍼런스콜 미흡 및 주주환원 정책 비판. 경영진 교체 요구.</t>
+          <t>주주 환원 정책 및 IR 발표 미흡에 대한 불만 제기. 경영진 및 이재용 관련 비판.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['컨퍼런스콜', '주주환원', '경영진']</t>
+          <t>['주주 환원', 'IR 발표', '경영진']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54900</v>
+        <v>55500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-10.59%</t>
+          <t>'-9.61%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G18" t="n">
-        <v>2118</v>
+        <v>2087</v>
       </c>
       <c r="H18" t="n">
         <v>22.34</v>
@@ -2082,7 +2082,7 @@
         <v>22.32</v>
       </c>
       <c r="O18" t="n">
-        <v>309700356700</v>
+        <v>316737609950</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>체코 원전 사업 관련 불확실성에도 불구하고 기자재 계약은 유지된다는 분석.</t>
+          <t>체코 원전 사업 협상 결렬에도 불구하고 두산 부품 사용 가능성 언급. 정치적 요인으로 인한 하락 가능성 시사.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['체코 원전', '기자재 계약', '협상 결렬']</t>
+          <t>['체코 원전', '협상 결렬', '두산 부품']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1834</v>
+        <v>1843</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-12.67%</t>
+          <t>'-12.24%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H19" t="n">
         <v>5.35</v>
@@ -2174,7 +2174,7 @@
         <v>5.07</v>
       </c>
       <c r="O19" t="n">
-        <v>13492471614</v>
+        <v>13593758373</v>
       </c>
       <c r="P19" t="n">
         <v>4980</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16580</v>
+        <v>16540</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-13.69%</t>
+          <t>'-13.90%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F20" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G20" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H20" t="n">
         <v>0.65</v>
@@ -2266,7 +2266,7 @@
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>91770078855</v>
+        <v>92049102765</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회에 따른 급락 가능성 경고.</t>
+          <t>보호예수 물량 해제에 따른 하락 위험 경고. 주포의 매도 가능성 및 반도체 섹터 조정 영향 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['보호예수', '물량 출회', '급락']</t>
+          <t>['보호예수', '주포 매도', '반도체 조정']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11740</v>
+        <v>11860</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-17.73%</t>
+          <t>'-16.89%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2329,10 +2329,10 @@
         <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="G21" t="n">
-        <v>2334</v>
+        <v>2370</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -2358,7 +2358,7 @@
         <v>9.83</v>
       </c>
       <c r="O21" t="n">
-        <v>299360638530</v>
+        <v>304701904240</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>체코 원전 사업 재협상 가능성 및 외국인 매수세 유입에 따른 단기 반등 기대.</t>
+          <t>체코 원전 사업 협상 결렬에 따른 단기 악재 발생. 다만, 외인 매수세 유입 및 정치적 요인 개입 가능성 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['체코 원전', '재협상', '외국인 매수']</t>
+          <t>['체코 원전', '협상 결렬', '외인 매수']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2095</v>
+        <v>2115</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-18.48%</t>
+          <t>'-17.70%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2450,7 +2450,7 @@
         <v>1.69</v>
       </c>
       <c r="O22" t="n">
-        <v>16405118182</v>
+        <v>16509997575</v>
       </c>
       <c r="P22" t="n">
         <v>2965</v>

--- a/data/trending_integrated_20261029_13.xlsx
+++ b/data/trending_integrated_20261029_13.xlsx
@@ -584,7 +584,7 @@
         <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>6867413179</v>
+        <v>6883760069</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9190</v>
+        <v>9180</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.02%</t>
+          <t>'+14.89%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H3" t="n">
         <v>17.97</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>128984333580</v>
+        <v>130231701460</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>광통신 섹터 내 대장주로서의 가능성 언급. 미국 시장 소폭 상승 및 루멘텀 급등 사례 참고.</t>
+          <t>광통신 섹터 내 상승 기대감. 미국발 훈풍 및 루멘텀 폭등 소식 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['광통신', '대장주', '루멘텀']</t>
+          <t>['광통신', '호재', '루멘텀']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,18 +751,18 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38250</v>
+        <v>38200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.91%</t>
+          <t>'+9.77%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.74</v>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
         <v>35</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>111261305600</v>
+        <v>112139505450</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8030</v>
+        <v>7840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.79%</t>
+          <t>'+5.23%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="F5" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G5" t="n">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>108650104600</v>
+        <v>110368060275</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>하이닉스 물량 완판 및 광주반도체 테마 관련 기대감. 외국인 및 기타법인 매수세 확인.</t>
+          <t>광주 반도체 테마 상승 기대감. 외국인 및 기타법인 매수세 유입 주장.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '테마', '외국인']</t>
+          <t>['광주 반도체', '테마주', '외국인 매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="G6" t="n">
-        <v>1381</v>
+        <v>1462</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.61</v>
       </c>
       <c r="O6" t="n">
-        <v>5274765255000</v>
+        <v>5333261294500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자 대비 경쟁 우위 확보 및 시총 1위 달성 전망. 4분기 실적 호조 기대감 언급.</t>
+          <t>SK하이닉스 실적 호조 및 삼성전자 대비 우위 전망. 국장 1황 지위 강조.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['경쟁 우위', '시총 1위', '실적 호조']</t>
+          <t>['SK하이닉스', '실적 호조', '삼성전자']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29100</v>
+        <v>29000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.39%</t>
+          <t>'+1.05%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1070,7 +1070,7 @@
         <v>1.73</v>
       </c>
       <c r="O7" t="n">
-        <v>103812101875</v>
+        <v>105075949700</v>
       </c>
       <c r="P7" t="n">
         <v>59600</v>
@@ -1130,13 +1130,13 @@
         <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F8" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G8" t="n">
-        <v>1800</v>
+        <v>1808</v>
       </c>
       <c r="H8" t="n">
         <v>24.78</v>
@@ -1162,7 +1162,7 @@
         <v>24.86</v>
       </c>
       <c r="O8" t="n">
-        <v>489743997500</v>
+        <v>497561103500</v>
       </c>
       <c r="P8" t="n">
         <v>723000</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14410</v>
+        <v>14450</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.14%</t>
+          <t>'+0.42%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F9" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G9" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H9" t="n">
         <v>8.050000000000001</v>
@@ -1254,7 +1254,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>53987090745</v>
+        <v>54227139735</v>
       </c>
       <c r="P9" t="n">
         <v>49800</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14920</v>
+        <v>14900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.40%</t>
+          <t>'-0.53%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F10" t="n">
         <v>87</v>
       </c>
       <c r="G10" t="n">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="H10" t="n">
         <v>3.33</v>
@@ -1346,7 +1346,7 @@
         <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>143545127195</v>
+        <v>144295155680</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>63500</v>
+        <v>26500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.09%</t>
+          <t>'-0.75%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.54</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>132</v>
+        <v>83</v>
       </c>
       <c r="F11" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="G11" t="n">
-        <v>640</v>
+        <v>340</v>
       </c>
       <c r="H11" t="n">
-        <v>41.55</v>
+        <v>12.23</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>64200</v>
+        <v>26700</v>
       </c>
       <c r="K11" t="n">
-        <v>64200</v>
+        <v>26350</v>
       </c>
       <c r="L11" t="n">
-        <v>65500</v>
+        <v>26600</v>
       </c>
       <c r="M11" t="n">
-        <v>62500</v>
+        <v>25450</v>
       </c>
       <c r="N11" t="n">
-        <v>41.01</v>
+        <v>12.3</v>
       </c>
       <c r="O11" t="n">
-        <v>161622817800</v>
+        <v>39313993025</v>
       </c>
       <c r="P11" t="n">
-        <v>67300</v>
+        <v>59300</v>
       </c>
       <c r="Q11" t="n">
-        <v>23150</v>
+        <v>22000</v>
       </c>
       <c r="R11" t="n">
-        <v>436000</v>
+        <v>-142000</v>
       </c>
       <c r="S11" t="n">
-        <v>-150000</v>
+        <v>-15000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>자사주 매입 및 소각 기대감에 따른 주가 상승 전망. 수주 공시 및 신고가 도전 가능성 언급.</t>
+          <t>실적 발표 앞두고 혼조세. 태양광 부문 전망 및 원전 관련 이슈 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['자사주 소각', '수주 공시', '신고가']</t>
+          <t>['실적 발표', '태양광', '원전']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26300</v>
+        <v>63400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.50%</t>
+          <t>'-1.25%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="G12" t="n">
-        <v>319</v>
+        <v>651</v>
       </c>
       <c r="H12" t="n">
-        <v>12.23</v>
+        <v>41.55</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,60 +1515,60 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>26700</v>
+        <v>64200</v>
       </c>
       <c r="K12" t="n">
-        <v>26350</v>
+        <v>64200</v>
       </c>
       <c r="L12" t="n">
-        <v>26600</v>
+        <v>65500</v>
       </c>
       <c r="M12" t="n">
-        <v>25450</v>
+        <v>62500</v>
       </c>
       <c r="N12" t="n">
-        <v>12.3</v>
+        <v>41.01</v>
       </c>
       <c r="O12" t="n">
-        <v>38539940800</v>
+        <v>164290529900</v>
       </c>
       <c r="P12" t="n">
-        <v>59300</v>
+        <v>67300</v>
       </c>
       <c r="Q12" t="n">
-        <v>22000</v>
+        <v>23150</v>
       </c>
       <c r="R12" t="n">
-        <v>-142000</v>
+        <v>436000</v>
       </c>
       <c r="S12" t="n">
-        <v>-15000</v>
+        <v>-150000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>실적 발표 예정 및 태양광 섹터 하락세 영향. 실적에 따른 매수 타이밍 고려 및 변동성 예상.</t>
+          <t>자사주 매입 및 소각 기대감에 따른 주가 상승 전망. 수주 공시 및 신고가 도전 가능성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적 발표', '태양광 섹터', '매수 타이밍']</t>
+          <t>['자사주 소각', '수주 공시', '신고가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
         <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H13" t="n">
         <v>0.37</v>
@@ -1622,7 +1622,7 @@
         <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>30466041160</v>
+        <v>30578338190</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16010</v>
+        <v>16020</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.03%</t>
+          <t>'-2.97%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="F14" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G14" t="n">
-        <v>446</v>
+        <v>501</v>
       </c>
       <c r="H14" t="n">
         <v>28.07</v>
@@ -1714,7 +1714,7 @@
         <v>28.03</v>
       </c>
       <c r="O14" t="n">
-        <v>51830670040</v>
+        <v>54549397780</v>
       </c>
       <c r="P14" t="n">
         <v>35350</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>실적 발표에 대한 부정적 전망 및 주가 하락 지속에 대한 우려.</t>
+          <t>실적 발표 후 주가 하락세. 조선주 전반의 부진 및 중국과의 경쟁력 약화 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적 발표', '주가 하락', '신저점']</t>
+          <t>['실적 발표', '조선주', '주가 하락']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F15" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G15" t="n">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="H15" t="n">
         <v>75</v>
@@ -1806,7 +1806,7 @@
         <v>74.90000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>1257792237700</v>
+        <v>1272139026600</v>
       </c>
       <c r="P15" t="n">
         <v>243500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주주 환원 불확실성 및 IR 발표 미흡에 대한 불만. 오너 리스크 및 증여세 관련 언급.</t>
+          <t>이재용 오너 리스크 및 주주환원 불확실성 우려. 우선주 매입 소각 기대감.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주주 환원', 'IR 발표', '오너 리스크']</t>
+          <t>['오너 리스크', '주주환원', '우선주']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4020</v>
+        <v>4000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.17%</t>
+          <t>'-4.65%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>81</v>
       </c>
       <c r="G16" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H16" t="n">
         <v>2.2</v>
@@ -1898,7 +1898,7 @@
         <v>1.2</v>
       </c>
       <c r="O16" t="n">
-        <v>164757568592</v>
+        <v>165275694497</v>
       </c>
       <c r="P16" t="n">
         <v>8100</v>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>230250</v>
+        <v>230000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.86%</t>
+          <t>'-4.96%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="G17" t="n">
-        <v>2143</v>
+        <v>2332</v>
       </c>
       <c r="H17" t="n">
         <v>46.19</v>
@@ -1990,7 +1990,7 @@
         <v>46.15</v>
       </c>
       <c r="O17" t="n">
-        <v>4423374987750</v>
+        <v>4485096330500</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주주 환원 정책 및 IR 발표 미흡에 대한 불만 제기. 경영진 및 이재용 관련 비판.</t>
+          <t>이재용 경영진 관련 논란 및 주주환원 정책 불만 제기. 코리아 디스카운트 원인 지목.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주주 환원', 'IR 발표', '경영진']</t>
+          <t>['이재용', '주주환원', '코리아 디스카운트']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55500</v>
+        <v>56100</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-9.61%</t>
+          <t>'-8.63%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="G18" t="n">
-        <v>2087</v>
+        <v>2056</v>
       </c>
       <c r="H18" t="n">
         <v>22.34</v>
@@ -2082,7 +2082,7 @@
         <v>22.32</v>
       </c>
       <c r="O18" t="n">
-        <v>316737609950</v>
+        <v>345141297050</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>체코 원전 사업 협상 결렬에도 불구하고 두산 부품 사용 가능성 언급. 정치적 요인으로 인한 하락 가능성 시사.</t>
+          <t>체코 원전 사업 재협상 결렬 관련 논란. 두산에너빌리티는 무관하다는 주장.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['체코 원전', '협상 결렬', '두산 부품']</t>
+          <t>['체코 원전', '재협상', '두산에너빌리티']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-12.24%</t>
+          <t>'-12.48%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H19" t="n">
         <v>5.35</v>
@@ -2174,7 +2174,7 @@
         <v>5.07</v>
       </c>
       <c r="O19" t="n">
-        <v>13593758373</v>
+        <v>13663910635</v>
       </c>
       <c r="P19" t="n">
         <v>4980</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16540</v>
+        <v>16530</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-13.90%</t>
+          <t>'-13.95%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="F20" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G20" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H20" t="n">
         <v>0.65</v>
@@ -2266,7 +2266,7 @@
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>92049102765</v>
+        <v>92735270115</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>보호예수 물량 해제에 따른 하락 위험 경고. 주포의 매도 가능성 및 반도체 섹터 조정 영향 언급.</t>
+          <t>보호예수 물량 해제 관련 하락 우려. 주가 조작 및 개미 털기 의혹 제기.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['보호예수', '주포 매도', '반도체 조정']</t>
+          <t>['보호예수', '하락', '주가 조작']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11860</v>
+        <v>11950</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-16.89%</t>
+          <t>'-16.26%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2329,10 +2329,10 @@
         <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="G21" t="n">
-        <v>2370</v>
+        <v>2342</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -2358,7 +2358,7 @@
         <v>9.83</v>
       </c>
       <c r="O21" t="n">
-        <v>304701904240</v>
+        <v>318963664100</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>체코 원전 사업 협상 결렬에 따른 단기 악재 발생. 다만, 외인 매수세 유입 및 정치적 요인 개입 가능성 언급.</t>
+          <t>체코 원전 사업 재협상 결렬에 따른 주가 하락 우려. 외인 매수세 유입 주장.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['체코 원전', '협상 결렬', '외인 매수']</t>
+          <t>['체코 원전', '재협상', '외인 매수']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2115</v>
+        <v>2120</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-17.70%</t>
+          <t>'-17.51%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2424,7 +2424,7 @@
         <v>62</v>
       </c>
       <c r="G22" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H22" t="n">
         <v>1.22</v>
@@ -2450,7 +2450,7 @@
         <v>1.69</v>
       </c>
       <c r="O22" t="n">
-        <v>16509997575</v>
+        <v>16683169781</v>
       </c>
       <c r="P22" t="n">
         <v>2965</v>

--- a/data/trending_integrated_20261029_13.xlsx
+++ b/data/trending_integrated_20261029_13.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5110</v>
+        <v>4940</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+29.86%</t>
+          <t>'+25.54%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>6883760069</v>
+        <v>7346528619</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -670,13 +670,13 @@
         <v>-0.67</v>
       </c>
       <c r="E3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H3" t="n">
         <v>17.97</v>
@@ -702,7 +702,7 @@
         <v>18.64</v>
       </c>
       <c r="O3" t="n">
-        <v>130231701460</v>
+        <v>131099205755</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>광통신 섹터 내 상승 기대감. 미국발 훈풍 및 루멘텀 폭등 소식 언급.</t>
+          <t>미국 광통신 기업 루멘텀 급등에 따른 동반 상승 기대. 광전자, 서울반도체와 함께 광통신 섹터 강세 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['광통신', '호재', '루멘텀']</t>
+          <t>['광통신', '루멘텀', '서울반도체']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38200</v>
+        <v>38150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+9.77%</t>
+          <t>'+9.63%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H4" t="n">
         <v>5.8</v>
@@ -794,7 +794,7 @@
         <v>6.54</v>
       </c>
       <c r="O4" t="n">
-        <v>112139505450</v>
+        <v>113104284625</v>
       </c>
       <c r="P4" t="n">
         <v>126600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7840</v>
+        <v>7870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.23%</t>
+          <t>'+5.64%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-1.04</v>
       </c>
       <c r="E5" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F5" t="n">
         <v>96</v>
       </c>
       <c r="G5" t="n">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="H5" t="n">
         <v>0.42</v>
@@ -886,7 +886,7 @@
         <v>1.46</v>
       </c>
       <c r="O5" t="n">
-        <v>110368060275</v>
+        <v>110720247735</v>
       </c>
       <c r="P5" t="n">
         <v>10300</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>광주 반도체 테마 상승 기대감. 외국인 및 기타법인 매수세 유입 주장.</t>
+          <t>광주 반도체 테마와 연계된 상승 기대감. 외국인 및 기타 법인 매수세 유입으로 인한 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1529000</v>
+        <v>1535000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.82%</t>
+          <t>'+3.23%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="G6" t="n">
-        <v>1462</v>
+        <v>1521</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.61</v>
       </c>
       <c r="O6" t="n">
-        <v>5333261294500</v>
+        <v>5406270846000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>SK하이닉스 실적 호조 및 삼성전자 대비 우위 전망. 국장 1황 지위 강조.</t>
+          <t>삼성전자와의 차별화된 실적 및 주주환원 정책에 대한 긍정적 전망. AI 반도체 시장 선도 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '실적 호조', '삼성전자']</t>
+          <t>['AI 반도체', '주주환원', '실적']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,18 +1027,18 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29000</v>
+        <v>28950</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.05%</t>
+          <t>'+0.87%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7" t="n">
         <v>27</v>
@@ -1070,7 +1070,7 @@
         <v>1.73</v>
       </c>
       <c r="O7" t="n">
-        <v>105075949700</v>
+        <v>105739433800</v>
       </c>
       <c r="P7" t="n">
         <v>59600</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>537000</v>
+        <v>538000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.56%</t>
+          <t>'+0.75%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>356</v>
       </c>
       <c r="F8" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G8" t="n">
-        <v>1808</v>
+        <v>1822</v>
       </c>
       <c r="H8" t="n">
         <v>24.78</v>
@@ -1162,7 +1162,7 @@
         <v>24.86</v>
       </c>
       <c r="O8" t="n">
-        <v>497561103500</v>
+        <v>505072423500</v>
       </c>
       <c r="P8" t="n">
         <v>723000</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14450</v>
+        <v>14460</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.42%</t>
+          <t>'+0.49%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>77</v>
       </c>
       <c r="G9" t="n">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="H9" t="n">
         <v>8.050000000000001</v>
@@ -1254,7 +1254,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>54227139735</v>
+        <v>54451415785</v>
       </c>
       <c r="P9" t="n">
         <v>49800</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>의료 AI 섹터 내 변동성 확대 및 공매도 관련 논란. 특정 가격대 이하 매수 구간 언급.</t>
+          <t>의료 AI 섹터 강세 및 공매도 세력에 대한 경고.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['의료 AI', '공매도', '변동성']</t>
+          <t>['의료 AI', '공매도', '헬스케어']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14900</v>
+        <v>14880</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.53%</t>
+          <t>'-0.67%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>150</v>
       </c>
       <c r="F10" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G10" t="n">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="H10" t="n">
         <v>3.33</v>
@@ -1346,7 +1346,7 @@
         <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>144295155680</v>
+        <v>144680490160</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26500</v>
+        <v>26450</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.75%</t>
+          <t>'-0.94%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="H11" t="n">
         <v>12.23</v>
@@ -1438,7 +1438,7 @@
         <v>12.3</v>
       </c>
       <c r="O11" t="n">
-        <v>39313993025</v>
+        <v>39808750650</v>
       </c>
       <c r="P11" t="n">
         <v>59300</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63400</v>
+        <v>63300</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.25%</t>
+          <t>'-1.40%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" t="n">
-        <v>651</v>
+        <v>669</v>
       </c>
       <c r="H12" t="n">
         <v>41.55</v>
@@ -1530,7 +1530,7 @@
         <v>41.01</v>
       </c>
       <c r="O12" t="n">
-        <v>164290529900</v>
+        <v>166395284750</v>
       </c>
       <c r="P12" t="n">
         <v>67300</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>자사주 매입 및 소각 기대감에 따른 주가 상승 전망. 수주 공시 및 신고가 도전 가능성 언급.</t>
+          <t>자사주 매입 및 소각 추진, 수주 공시를 통한 신고가 도전 기대. 삼성전자 투자 확대 수혜 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8920</v>
+        <v>8940</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.83%</t>
+          <t>'-2.61%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H13" t="n">
         <v>0.37</v>
@@ -1622,7 +1622,7 @@
         <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>30578338190</v>
+        <v>30635177220</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16020</v>
+        <v>184300</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.97%</t>
+          <t>'-3.05%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F14" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="G14" t="n">
-        <v>501</v>
+        <v>565</v>
       </c>
       <c r="H14" t="n">
-        <v>28.07</v>
+        <v>75</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>16510</v>
+        <v>190100</v>
       </c>
       <c r="K14" t="n">
-        <v>16380</v>
+        <v>189400</v>
       </c>
       <c r="L14" t="n">
-        <v>16440</v>
+        <v>197000</v>
       </c>
       <c r="M14" t="n">
-        <v>15750</v>
+        <v>180800</v>
       </c>
       <c r="N14" t="n">
-        <v>28.03</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>54549397780</v>
+        <v>1288540985800</v>
       </c>
       <c r="P14" t="n">
-        <v>35350</v>
+        <v>243500</v>
       </c>
       <c r="Q14" t="n">
-        <v>15750</v>
+        <v>71000</v>
       </c>
       <c r="R14" t="n">
-        <v>-22000</v>
+        <v>-1183000</v>
       </c>
       <c r="S14" t="n">
-        <v>-310000</v>
+        <v>-148000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>실적 발표 후 주가 하락세. 조선주 전반의 부진 및 중국과의 경쟁력 약화 우려.</t>
+          <t>이재용 오너 리스크와 주주환원 불확실성에 대한 부정적 전망. 우선주 매입 소각 기대감 있으나 확정적이지 않음.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적 발표', '조선주', '주가 하락']</t>
+          <t>['우선주', '주주환원', '오너 리스크']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>184100</v>
+        <v>15970</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.16%</t>
+          <t>'-3.27%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="F15" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G15" t="n">
-        <v>552</v>
+        <v>518</v>
       </c>
       <c r="H15" t="n">
-        <v>75</v>
+        <v>28.07</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>190100</v>
+        <v>16510</v>
       </c>
       <c r="K15" t="n">
-        <v>189400</v>
+        <v>16380</v>
       </c>
       <c r="L15" t="n">
-        <v>197000</v>
+        <v>16440</v>
       </c>
       <c r="M15" t="n">
-        <v>180800</v>
+        <v>15750</v>
       </c>
       <c r="N15" t="n">
-        <v>74.90000000000001</v>
+        <v>28.03</v>
       </c>
       <c r="O15" t="n">
-        <v>1272139026600</v>
+        <v>55900123695</v>
       </c>
       <c r="P15" t="n">
-        <v>243500</v>
+        <v>35350</v>
       </c>
       <c r="Q15" t="n">
-        <v>71000</v>
+        <v>15750</v>
       </c>
       <c r="R15" t="n">
-        <v>-1183000</v>
+        <v>-22000</v>
       </c>
       <c r="S15" t="n">
-        <v>-148000</v>
+        <v>-310000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>이재용 오너 리스크 및 주주환원 불확실성 우려. 우선주 매입 소각 기대감.</t>
+          <t>실적 발표 후 주가 하락세. 조선주 전반의 부진 및 중국과의 경쟁력 약화 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['오너 리스크', '주주환원', '우선주']</t>
+          <t>['실적 발표', '조선주', '주가 하락']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4000</v>
+        <v>3990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.65%</t>
+          <t>'-4.89%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F16" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G16" t="n">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="H16" t="n">
         <v>2.2</v>
@@ -1898,7 +1898,7 @@
         <v>1.2</v>
       </c>
       <c r="O16" t="n">
-        <v>165275694497</v>
+        <v>165717017819</v>
       </c>
       <c r="P16" t="n">
         <v>8100</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>5G 상용화 및 글로벌 기업 공급 관련 뉴스 언급. 광통신 섹터 주도주 가능성.</t>
+          <t>5G 상용화망 성공 및 글로벌 기업 공급 시작에 따른 기대감. 광통신 섹터 강세와 함께 급등 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['5G', '광통신', '수주']</t>
+          <t>['5G', '광통신', '글로벌 공급']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>230000</v>
+        <v>229750</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.96%</t>
+          <t>'-5.06%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>540</v>
+        <v>518</v>
       </c>
       <c r="G17" t="n">
-        <v>2332</v>
+        <v>2428</v>
       </c>
       <c r="H17" t="n">
         <v>46.19</v>
@@ -1990,7 +1990,7 @@
         <v>46.15</v>
       </c>
       <c r="O17" t="n">
-        <v>4485096330500</v>
+        <v>4549935581750</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>이재용 경영진 관련 논란 및 주주환원 정책 불만 제기. 코리아 디스카운트 원인 지목.</t>
+          <t>이재용 관련 사법 리스크와 주주환원 불확실성으로 인한 주가 하락 우려. 코리아 디스카운트 원흉 지적.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['이재용', '주주환원', '코리아 디스카운트']</t>
+          <t>['오너 리스크', '주주환원', '컨퍼콜']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56100</v>
+        <v>55700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.63%</t>
+          <t>'-9.28%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="G18" t="n">
-        <v>2056</v>
+        <v>2005</v>
       </c>
       <c r="H18" t="n">
         <v>22.34</v>
@@ -2082,7 +2082,7 @@
         <v>22.32</v>
       </c>
       <c r="O18" t="n">
-        <v>345141297050</v>
+        <v>352352478400</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>체코 원전 사업 재협상 결렬 관련 논란. 두산에너빌리티는 무관하다는 주장.</t>
+          <t>체코 원전 사업 입찰 결렬에도 두산에너빌리티는 무관하다는 해명 공시. 일부 언론의 허위 기사에 대한 비판.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['체코 원전', '재협상', '두산에너빌리티']</t>
+          <t>['체코 원전', '해명 공시', '두산에너빌리티']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1838</v>
+        <v>1841</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-12.48%</t>
+          <t>'-12.33%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="H19" t="n">
         <v>5.35</v>
@@ -2174,7 +2174,7 @@
         <v>5.07</v>
       </c>
       <c r="O19" t="n">
-        <v>13663910635</v>
+        <v>13745484541</v>
       </c>
       <c r="P19" t="n">
         <v>4980</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16530</v>
+        <v>16420</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-13.95%</t>
+          <t>'-14.52%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F20" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G20" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H20" t="n">
         <v>0.65</v>
@@ -2266,7 +2266,7 @@
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>92735270115</v>
+        <v>93083261225</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11950</v>
+        <v>11830</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-16.26%</t>
+          <t>'-17.10%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2329,10 +2329,10 @@
         <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="G21" t="n">
-        <v>2342</v>
+        <v>2355</v>
       </c>
       <c r="H21" t="n">
         <v>9.6</v>
@@ -2358,7 +2358,7 @@
         <v>9.83</v>
       </c>
       <c r="O21" t="n">
-        <v>318963664100</v>
+        <v>323636882315</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>체코 원전 사업 재협상 결렬에 따른 주가 하락 우려. 외인 매수세 유입 주장.</t>
+          <t>체코 원전 사업 재협상 불발에 따른 감액 논란. 외인 매수세 유입으로 단기 반등 기대.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['체코 원전', '재협상', '외인 매수']</t>
+          <t>['체코 원전', '재협상', '감액']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2450,7 +2450,7 @@
         <v>1.69</v>
       </c>
       <c r="O22" t="n">
-        <v>16683169781</v>
+        <v>16731327043</v>
       </c>
       <c r="P22" t="n">
         <v>2965</v>
